--- a/table2.xlsx
+++ b/table2.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t xml:space="preserve">
 </t>
@@ -37,7 +37,7 @@
     <t xml:space="preserve">    stage 2</t>
   </si>
   <si>
-    <t xml:space="preserve">n/N (%)</t>
+    <t xml:space="preserve">n (%)</t>
   </si>
   <si>
     <t xml:space="preserve">Abbreviation: CI = Confidence Interval</t>
@@ -47,193 +47,108 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">25-39
-N = 1600137 (32%)
+    <t xml:space="preserve">Overall
+N = 4953759
 </t>
   </si>
   <si>
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">462,089.00/1,600,137.00 (28.88%) (28.81%, 28.95%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">204,097.00/1,600,137.00 (12.75%) (12.70%, 12.81%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">587,436.00/1,600,137.00 (36.71%) (36.64%, 36.79%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">346,515.00/1,600,137.00 (21.66%) (21.59%, 21.72%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40-
-N = 3353622 (68%)
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">475,158.00/3,353,622.00 (14.17%) (14.13%, 14.21%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">328,362.00/3,353,622.00 (9.79%) (9.759%, 9.823%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,139,513.00/3,353,622.00 (33.98%) (33.93%, 34.03%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,410,589.00/3,353,622.00 (42.06%) (42.01%, 42.11%)</t>
+    <t xml:space="preserve">937,247 (18.92%) (18.9%, 19.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">532,459 (10.75%) (10.7%, 10.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,726,949 (34.86%) (34.8%, 34.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,757,104 (35.47%) (35.4%, 35.5%)</t>
   </si>
   <si>
     <t xml:space="preserve">Micro-Metropolitan
 </t>
   </si>
   <si>
-    <t xml:space="preserve">25-39
-N = 186357 (29%)
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43,020.00/186,357.00 (23.08%) (22.89%, 23.28%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23,421.00/186,357.00 (12.57%) (12.42%, 12.72%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70,116.00/186,357.00 (37.62%) (37.40%, 37.85%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49,800.00/186,357.00 (26.72%) (26.52%, 26.92%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40-
-N = 465113 (71%)
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49,441.00/465,113.00 (10.63%) (10.54%, 10.72%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41,782.00/465,113.00 (8.98%) (8.901%, 9.066%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150,029.00/465,113.00 (32.26%) (32.12%, 32.39%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">223,861.00/465,113.00 (48.13%) (47.99%, 48.27%)</t>
+    <t xml:space="preserve">Overall
+N = 651470
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92,461 (14.19%) (14.1%, 14.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65,203 (10.01%) (9.94%, 10.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">220,145 (33.79%) (33.7%, 33.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">273,661 (42.01%) (41.9%, 42.1%)</t>
   </si>
   <si>
     <t xml:space="preserve">Small Town
 </t>
   </si>
   <si>
-    <t xml:space="preserve">25-39
-N = 85980 (27%)
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18,851.00/85,980.00 (21.92%) (21.65%, 22.20%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10,746.00/85,980.00 (12.50%) (12.28%, 12.72%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32,483.00/85,980.00 (37.78%) (37.46%, 38.10%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23,900.00/85,980.00 (27.80%) (27.50%, 28.10%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40-
-N = 231489 (73%)
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22,912.00/231,489.00 (9.90%) (9.776%, 10.02%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20,164.00/231,489.00 (8.71%) (8.596%, 8.826%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72,849.00/231,489.00 (31.47%) (31.28%, 31.66%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115,564.00/231,489.00 (49.92%) (49.72%, 50.13%)</t>
+    <t xml:space="preserve">Overall
+N = 317469
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41,763 (13.15%) (13.0%, 13.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30,910 (9.74%) (9.63%, 9.84%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105,332 (33.18%) (33.0%, 33.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139,464 (43.93%) (43.8%, 44.1%)</t>
   </si>
   <si>
     <t xml:space="preserve">Rural
 </t>
   </si>
   <si>
-    <t xml:space="preserve">25-39
-N = 64750 (25%)
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14,509.00/64,750.00 (22.41%) (22.09%, 22.73%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7,883.00/64,750.00 (12.17%) (11.92%, 12.43%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24,353.00/64,750.00 (37.61%) (37.24%, 37.99%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18,005.00/64,750.00 (27.81%) (27.46%, 28.15%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40-
-N = 196245 (75%)
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18,799.00/196,245.00 (9.58%) (9.450%, 9.711%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16,445.00/196,245.00 (8.38%) (8.258%, 8.503%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60,551.00/196,245.00 (30.85%) (30.65%, 31.06%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100,450.00/196,245.00 (51.19%) (50.96%, 51.41%)</t>
+    <t xml:space="preserve">Overall
+N = 260995
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33,308 (12.76%) (12.6%, 12.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24,328 (9.32%) (9.21%, 9.43%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84,904 (32.53%) (32.4%, 32.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118,455 (45.39%) (45.2%, 45.6%)</t>
   </si>
   <si>
     <t xml:space="preserve">NA
 </t>
   </si>
   <si>
-    <t xml:space="preserve">25-39
-N = 3736 (42%)
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,117.00/3,736.00 (29.90%) (28.44%, 31.40%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">496.00/3,736.00 (13.28%) (12.21%, 14.42%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,395.00/3,736.00 (37.34%) (35.79%, 38.92%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">728.00/3,736.00 (19.49%) (18.23%, 20.80%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40-
-N = 5225 (58%)
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">971.00/5,225.00 (18.58%) (17.54%, 19.67%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">577.00/5,225.00 (11.04%) (10.21%, 11.93%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,872.00/5,225.00 (35.83%) (34.53%, 37.15%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,805.00/5,225.00 (34.55%) (33.26%, 35.86%)</t>
+    <t xml:space="preserve">Overall
+N = 8961
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,088 (23.30%) (22.4%, 24.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,073 (11.97%) (11.3%, 12.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,267 (36.46%) (35.5%, 37.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,533 (28.27%) (27.3%, 29.2%)</t>
   </si>
 </sst>
 </file>
@@ -699,11 +614,6 @@
     <col min="4" max="4" width="10.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="10.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="10.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="10.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="10.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="10.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="10.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="10.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="NA" customHeight="1">
@@ -714,31 +624,16 @@
         <v>9</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" ht="NA" customHeight="1">
@@ -749,31 +644,16 @@
         <v>10</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="K2" s="9" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" ht="NA" customHeight="1">
@@ -795,21 +675,6 @@
       <c r="F3" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="J3" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="K3" s="10" t="s">
-        <v>11</v>
-      </c>
     </row>
     <row r="4" ht="NA" customHeight="1">
       <c r="A4" s="4" t="s">
@@ -819,31 +684,16 @@
         <v>12</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="J4" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="K4" s="11" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" ht="NA" customHeight="1">
@@ -854,31 +704,16 @@
         <v>13</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="K5" s="11" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" ht="NA" customHeight="1">
@@ -889,31 +724,16 @@
         <v>14</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="H6" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="K6" s="11" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" ht="NA" customHeight="1">
@@ -924,31 +744,16 @@
         <v>15</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="H7" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="I7" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="J7" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="K7" s="12" t="s">
-        <v>64</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" ht="NA" customHeight="1">
@@ -970,21 +775,6 @@
       <c r="F8" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G8" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="K8" s="6" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="9" ht="NA" customHeight="1">
       <c r="A9" s="7" t="s">
@@ -1005,31 +795,11 @@
       <c r="F9" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="G9" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>8</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A8:K8"/>
-    <mergeCell ref="A9:K9"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/table2.xlsx
+++ b/table2.xlsx
@@ -165,13 +165,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <b/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>

--- a/table2.xlsx
+++ b/table2.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
   <si>
     <t xml:space="preserve">
 </t>
@@ -40,115 +40,197 @@
     <t xml:space="preserve">n (%)</t>
   </si>
   <si>
-    <t xml:space="preserve">Abbreviation: CI = Confidence Interval</t>
-  </si>
-  <si>
     <t xml:space="preserve">Metropolitan
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Overall
-N = 4953759
+    <t xml:space="preserve">25-39
+N = 1600137 (32%)
 </t>
   </si>
   <si>
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">937,247 (18.92%) (18.9%, 19.0%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">532,459 (10.75%) (10.7%, 10.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,726,949 (34.86%) (34.8%, 34.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,757,104 (35.47%) (35.4%, 35.5%)</t>
+    <t xml:space="preserve">462,089 (28.88%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">204,097 (12.75%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">587,436 (36.71%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">346,515 (21.66%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40-
+N = 3353622 (68%)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">475,158 (14.17%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">328,362 (9.79%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,139,513 (33.98%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,410,589 (42.06%)</t>
   </si>
   <si>
     <t xml:space="preserve">Micro-Metropolitan
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Overall
-N = 651470
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92,461 (14.19%) (14.1%, 14.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65,203 (10.01%) (9.94%, 10.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">220,145 (33.79%) (33.7%, 33.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">273,661 (42.01%) (41.9%, 42.1%)</t>
+    <t xml:space="preserve">25-39
+N = 186357 (29%)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43,020 (23.08%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23,421 (12.57%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70,116 (37.62%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49,800 (26.72%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40-
+N = 465113 (71%)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49,441 (10.63%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41,782 (8.98%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150,029 (32.26%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">223,861 (48.13%)</t>
   </si>
   <si>
     <t xml:space="preserve">Small Town
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Overall
-N = 317469
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41,763 (13.15%) (13.0%, 13.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30,910 (9.74%) (9.63%, 9.84%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105,332 (33.18%) (33.0%, 33.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139,464 (43.93%) (43.8%, 44.1%)</t>
+    <t xml:space="preserve">25-39
+N = 85980 (27%)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18,851 (21.92%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10,746 (12.50%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32,483 (37.78%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23,900 (27.80%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40-
+N = 231489 (73%)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22,912 (9.90%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20,164 (8.71%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72,849 (31.47%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115,564 (49.92%)</t>
   </si>
   <si>
     <t xml:space="preserve">Rural
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Overall
-N = 260995
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33,308 (12.76%) (12.6%, 12.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24,328 (9.32%) (9.21%, 9.43%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84,904 (32.53%) (32.4%, 32.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118,455 (45.39%) (45.2%, 45.6%)</t>
+    <t xml:space="preserve">25-39
+N = 64750 (25%)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14,509 (22.41%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,883 (12.17%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24,353 (37.61%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18,005 (27.81%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40-
+N = 196245 (75%)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18,799 (9.58%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16,445 (8.38%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60,551 (30.85%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100,450 (51.19%)</t>
   </si>
   <si>
     <t xml:space="preserve">NA
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Overall
-N = 8961
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,088 (23.30%) (22.4%, 24.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,073 (11.97%) (11.3%, 12.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,267 (36.46%) (35.5%, 37.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,533 (28.27%) (27.3%, 29.2%)</t>
+    <t xml:space="preserve">25-39
+N = 3736 (42%)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,117 (29.90%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">496 (13.28%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,395 (37.34%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">728 (19.49%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40-
+N = 5225 (58%)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">971 (18.58%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">577 (11.04%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,872 (35.83%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,805 (34.55%)</t>
   </si>
 </sst>
 </file>
@@ -184,7 +266,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -258,20 +340,6 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
       <bottom style="none">
         <color rgb="FF000000"/>
       </bottom>
@@ -280,7 +348,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment textRotation="0" horizontal="left" vertical="top" wrapText="1"/>
@@ -298,9 +366,6 @@
       <alignment textRotation="0" horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="0" horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment textRotation="0" horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -614,146 +679,256 @@
     <col min="4" max="4" width="10.71" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="10.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="10.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="10.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="10.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="10.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="10.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="10.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="NA" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>34</v>
+      <c r="B1" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="2" ht="NA" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>35</v>
+      <c r="B2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="3" ht="NA" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>11</v>
+      <c r="B3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="4" ht="NA" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>36</v>
+      <c r="B4" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="5" ht="NA" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>37</v>
+      <c r="B5" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="6" ht="NA" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>38</v>
+      <c r="B6" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="K6" s="10" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="7" ht="NA" customHeight="1">
       <c r="A7" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>39</v>
+      <c r="B7" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="8" ht="NA" customHeight="1">
@@ -775,31 +950,30 @@
       <c r="F8" s="6" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" ht="NA" customHeight="1">
-      <c r="A9" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>8</v>
+      <c r="G8" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A9:F9"/>
+  <mergeCells count="6">
+    <mergeCell ref="A8:K8"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
